--- a/云平台远程连接接口文档.xlsx
+++ b/云平台远程连接接口文档.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,9 @@
       <name val="微软雅黑"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00FFFF00"/>
     </font>
   </fonts>
   <fills count="3">
@@ -85,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +99,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -647,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -956,6 +960,83 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>定位初始化</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>mower/{设备ID}/cmd/init_location</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>云平台→割草机</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>{"action": "request"}</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>request/confirm/cancel</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>request=请求初始化；confirm=确认后开始走8字形；cancel=取消</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>需先 request 再 confirm，confirm 后车辆立即移动</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>{"action": "confirm"}</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>{"action": "cancel"}</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1268,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1426,6 +1507,23 @@
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>udp_com_main 节点发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>cmd/init_location</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>收到 request 转发 /signal = "init_location"；收到 confirm 转发 /signal = "true"；收到 cancel 转发 /signal = "false"</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>task_node 控制车辆走8字形完成定位初始化</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1564,6 +1662,42 @@
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/task' -m '{"action":"stop"}'</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>联调示例-请求定位初始化</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/init_location' -m '{"action":"request"}'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>联调示例-确认定位初始化</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/init_location' -m '{"action":"confirm"}'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>联调示例-取消定位初始化</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/init_location' -m '{"action":"cancel"}'</t>
         </is>
       </c>
     </row>

--- a/云平台远程连接接口文档.xlsx
+++ b/云平台远程连接接口文档.xlsx
@@ -42,11 +42,13 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00C00000"/>
+      <color rgb="000070C0"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00FFFF00"/>
+      <name val="微软雅黑"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -99,7 +101,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -962,81 +966,125 @@
       <c r="I8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>定位初始化</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>mower/{设备ID}/cmd/init_location</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>云平台→割草机</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>{"action": "request"}</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>request/confirm/cancel</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>request=请求初始化；confirm=确认后开始走8字形；cancel=取消</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>需先 request 再 confirm，confirm 后车辆立即移动</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>request=请求定位初始化；confirm=确认（车辆开始走8字形动作）；cancel=取消</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>云平台下发request并确认场地安全后再下发confirm，车辆才开始走8字形；初始化过程中可随时cancel</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>{"action": "confirm"}</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>建图控制</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>mower/{设备ID}/cmd/mapping</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>云平台→割草机</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>{"action": "enter"}</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>enter/start_boundary/stop_boundary/start_obstacle/stop_obstacle/start_parking/stop_parking/start_path/stop_path/save/delete/list/reset</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>建图操作，详见下方说明</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>建图过程中车辆完全由云平台遥控（cmd/move），建图页面需集成遥控功能。建图流程：① 下发 enter 进入建图模式（车端发 m_mode 通知雷达/RTK准备，随后定位坐标会被外部系统归零为(0,0,0)）；② 观察 state/mapping，等定位状态有效(state为1/2/5)且 x、y 归零到(0,0)附近后，下发 start_boundary；③ 遥控车沿边界行驶，云平台用 state/mapping 轨迹流实时描边；④ 到终点下发 stop_boundary，如需障碍物/停车位/连接路径按需重复 start/stop；⑤ 下发 save 保存地图，保存后本次建图会话结束。注意：录制过程中请勿下发 blade/task 等其他指令，否则车端会中断当前录制</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>{"action": "cancel"}</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>map_name</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>string(save/delete时)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>不能含 / 和 ..</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>要保存或删除的地图名</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1049,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1338,6 +1386,188 @@
       </c>
       <c r="I9" s="2" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>建图轨迹</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>mower/{设备ID}/state/mapping</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>割草机→云平台</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>与 state/location 相同(默认10Hz)，仅建图会话期间上报</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>{"x":0.0,"y":0.0,"z":0.0,"roll":0.01,"pitch":-0.02,"yaw":1.57,"state":4,"stamp":1751356800.6}</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>x / y / z</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>局部平面坐标(米)，即建图期间车辆走过的轨迹</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>从收到 cmd/mapping enter 起，到 save 或 reset 止；字段含义与 state/location 完全一致。云平台建图页面用它实时描出行驶轨迹（即正在录制的边界走向），并据此观察 enter 之后坐标是否已归零</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>roll / pitch / yaw</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>姿态(弧度)</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>定位状态字：0=无定位；1/2/5=有效融合定位</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>stamp</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Unix秒(double)</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>地图列表</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>mower/{设备ID}/state/map_list</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>割草机→云平台</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>收到 cmd/mapping list 后回传一次</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>{"maps":["map_0630","map_0701"],"stamp":1751356800.8}</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>maps</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>array&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>车端已保存的地图名列表</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>stamp</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Unix秒(double)</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1349,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1511,19 +1741,121 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>cmd/init_location</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>收到 request 转发 /signal = "init_location"；收到 confirm 转发 /signal = "true"；收到 cancel 转发 /signal = "false"</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>task_node 控制车辆走8字形完成定位初始化</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>/signal = init_location / true / false</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_node 定位初始化流程（8字动作），外部定位系统重启定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>cmd/mapping enter</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>/signal = m_mode</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>雷达/RTK进入建图准备，定位坐标由外部系统归零</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>cmd/mapping start/stop_boundary等</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>/signal = start_brd/cease_brd/start_obs/cease_obs 等</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>location_map 录制边界/障碍物/停车位/连接路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>cmd/mapping save/delete</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>/signal = save_map|delete_name/地图名</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>location_map 保存/删除地图文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>cmd/mapping list</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>/signal = p_mode</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>location_map 发布 /map_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>建图轨迹上报</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>建图会话期间（enter→save/reset）转发 /Mower/position 到 state/mapping</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>外部定位模块发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>地图列表</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>订阅 /map_name，解析后转发 state/map_list</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>location_map 发布</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1666,38 +1998,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>联调示例-请求定位初始化</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/init_location' -m '{"action":"request"}'</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>联调示例-进入建图模式</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/mapping' -m '{"action":"enter"}'</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>联调示例-确认定位初始化</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/init_location' -m '{"action":"confirm"}'</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>联调示例-开始录制边界</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/mapping' -m '{"action":"start_boundary"}'</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>联调示例-取消定位初始化</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/init_location' -m '{"action":"cancel"}'</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>联调示例-停止录制边界</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/mapping' -m '{"action":"stop_boundary"}'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>联调示例-保存地图</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/mapping' -m '{"action":"save","map_name":"map_0701"}'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>联调示例-请求地图列表</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>mosquitto_pub -h &lt;broker&gt; -t 'mower/mower_001/cmd/mapping' -m '{"action":"list"}'</t>
         </is>
       </c>
     </row>
@@ -1756,164 +2112,164 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>以下接口已于 2026-09-11 从车端 cloud_bridge 中删除，云平台请勿再使用：</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>视频控制（已删除）</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>mower/{设备ID}/cmd/video</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>{"enable": true, "fps": 5, "width": 640, "height": 480, "bitrate": 800}</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>enable</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>true/false；开启/关闭 SRT 推流</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>0.1 ~ 30；推流帧率</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>width / height</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>16~1920 / 16~1080；输出分辨率</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>bitrate</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>100 ~ 8000；H.264 码率 kbps</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>整条 SRT 视频通道（H.264 + MPEG-TS，车端 caller 推流）已随本接口一并移除，车端不再订阅 /camera/image_rect，launch 中 srt_target/video_* 参数均已删除</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>车辆状态已删字段</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>mower/{设备ID}/state/vehicle</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>left_wheel_speed</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>左轮速度（原来自 /vehicle/left_wheel_speed）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>right_wheel_speed</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>右轮速度（原来自 /vehicle/right_wheel_speed）</t>
         </is>

--- a/云平台远程连接接口文档.xlsx
+++ b/云平台远程连接接口文档.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,11 @@
     <font>
       <name val="微软雅黑"/>
       <color rgb="000070C0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="0000B050"/>
       <sz val="10"/>
     </font>
     <font>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,6 +107,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1097,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1568,6 +1576,168 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>地图原点</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>mower/{设备ID}/state/map_origin</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>割草机→云平台</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>收到 /signal 选图信号 use_map/编号 时回传一次</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>{"map_name":"map_0630","found":true,"map_index":0,"latitude":28.236557,"longitude":112.876617,"height":86.60,"gauss_yaw":73.89,"stamp":1751356800.9}</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>map_name</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>请求的地图编号</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>车端订阅 /signal，匹配 use_map/编号 时从 map_dir(launch可配) 读取 &lt;编号&gt;.mp 原点文件并上发；cmd/task start 带 map_name、安卓端选图均会触发。云平台可据此把 state/location 的局部坐标换算成经纬度</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>found</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>是否找到并解析成功；文件缺失时为false（此时无以下字段）</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>map_index</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>地图内部索引</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>latitude / longitude / height</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>地图原点 WGS84 纬度/经度/椭球高(米)</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>gauss_yaw</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>建图时的高斯坐标系偏航角(度)</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>stamp</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Unix秒(double)</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1579,7 +1749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1856,6 +2026,23 @@
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>location_map 发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>地图原点</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>订阅 /signal，匹配 use_map/编号 时读取 map_dir/&lt;编号&gt;.mp，回传 state/map_origin</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>cloud_bridge 直接读 fusion 的 .mp 原点文件</t>
         </is>
       </c>
     </row>
@@ -2112,164 +2299,164 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>以下接口已于 2026-09-11 从车端 cloud_bridge 中删除，云平台请勿再使用：</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr"/>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>视频控制（已删除）</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>mower/{设备ID}/cmd/video</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>{"enable": true, "fps": 5, "width": 640, "height": 480, "bitrate": 800}</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>enable</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>true/false；开启/关闭 SRT 推流</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>0.1 ~ 30；推流帧率</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>width / height</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>16~1920 / 16~1080；输出分辨率</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>bitrate</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>100 ~ 8000；H.264 码率 kbps</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>整条 SRT 视频通道（H.264 + MPEG-TS，车端 caller 推流）已随本接口一并移除，车端不再订阅 /camera/image_rect，launch 中 srt_target/video_* 参数均已删除</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>车辆状态已删字段</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>mower/{设备ID}/state/vehicle</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>left_wheel_speed</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>左轮速度（原来自 /vehicle/left_wheel_speed）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>right_wheel_speed</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>右轮速度（原来自 /vehicle/right_wheel_speed）</t>
         </is>
